--- a/templates/admin.xlsx
+++ b/templates/admin.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nhuan\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5EAD247-171B-423A-8B81-D01AE1996C47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF12DF29-1F24-4610-9DB2-B51ACBE1B307}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BaoCao_Mau" sheetId="1" r:id="rId1"/>
@@ -37,10 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="39">
-  <si>
-    <t>BÁO CÁO HIỆN TRẠNG SỬ DỤNG NƯỚC SẠCH CẤP XÃ/PHƯỜNG</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="38">
   <si>
     <t>STT</t>
   </si>
@@ -78,12 +75,6 @@
     <t>DỮ LIỆU CHÍNH</t>
   </si>
   <si>
-    <t>Lưu ý thiết kế</t>
-  </si>
-  <si>
-    <t>Mẫu này ưu tiên validation cơ bản nhưng có sẵn vùng cấu hình dòng 4–9 để Portal đọc quy tắc về sau.</t>
-  </si>
-  <si>
     <t>Mục</t>
   </si>
   <si>
@@ -154,24 +145,25 @@
   </si>
   <si>
     <t>asdfasdfa sdfa</t>
+  </si>
+  <si>
+    <t>BÁO CÁO QUNAA</t>
+  </si>
+  <si>
+    <t>ÀAS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <name val="Arial"/>
     </font>
     <font>
       <b/>
@@ -183,8 +175,29 @@
       <sz val="11"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -206,6 +219,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -237,15 +256,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -256,23 +271,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -577,7 +591,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:K38"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.625" customWidth="1"/>
@@ -594,321 +608,321 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+    </row>
+    <row r="2" spans="1:11" ht="30" x14ac:dyDescent="0.2">
+      <c r="A2" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-    </row>
-    <row r="2" spans="1:11" ht="30" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
+      <c r="B2" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="2" t="s">
+    </row>
+    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="15" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="7"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
+    </row>
+    <row r="5" spans="1:11" ht="15" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="7"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
+    </row>
+    <row r="6" spans="1:11" ht="15" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="7"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+    </row>
+    <row r="7" spans="1:11" ht="15" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="7"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+    </row>
+    <row r="8" spans="1:11" ht="28.5" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="7"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+    </row>
+    <row r="9" spans="1:11" ht="28.5" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="7"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
+    </row>
+    <row r="10" spans="1:11" ht="15" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="7"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
+    </row>
+    <row r="11" spans="1:11" ht="15" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="7"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+    </row>
+    <row r="12" spans="1:11" ht="15" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="7"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+    </row>
+    <row r="13" spans="1:11" ht="15" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="7"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
+      <c r="K13" s="8"/>
+    </row>
+    <row r="14" spans="1:11" ht="15" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="7"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
+    </row>
+    <row r="15" spans="1:11" ht="15" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="7"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
+      <c r="K15" s="8"/>
+    </row>
+    <row r="16" spans="1:11" ht="15" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="7"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
+    </row>
+    <row r="17" spans="1:11" ht="15" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="7"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8"/>
+    </row>
+    <row r="18" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A3" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J3" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="K3" s="8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="15" x14ac:dyDescent="0.2">
-      <c r="A4" s="9"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="I4" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
-    </row>
-    <row r="5" spans="1:11" ht="15" x14ac:dyDescent="0.2">
-      <c r="A5" s="9"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="I5" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
-    </row>
-    <row r="6" spans="1:11" ht="15" x14ac:dyDescent="0.2">
-      <c r="A6" s="9"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10"/>
-    </row>
-    <row r="7" spans="1:11" ht="15" x14ac:dyDescent="0.2">
-      <c r="A7" s="9"/>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-    </row>
-    <row r="8" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A8" s="9"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="J8" s="10"/>
-      <c r="K8" s="10"/>
-    </row>
-    <row r="9" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A9" s="9"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10"/>
-    </row>
-    <row r="10" spans="1:11" ht="15" x14ac:dyDescent="0.2">
-      <c r="A10" s="9"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10"/>
-    </row>
-    <row r="11" spans="1:11" ht="15" x14ac:dyDescent="0.2">
-      <c r="A11" s="9"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
-    </row>
-    <row r="12" spans="1:11" ht="15" x14ac:dyDescent="0.2">
-      <c r="A12" s="9"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10"/>
-      <c r="K12" s="10"/>
-    </row>
-    <row r="13" spans="1:11" ht="15" x14ac:dyDescent="0.2">
-      <c r="A13" s="9"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10"/>
-      <c r="K13" s="10"/>
-    </row>
-    <row r="14" spans="1:11" ht="15" x14ac:dyDescent="0.2">
-      <c r="A14" s="9"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10"/>
-      <c r="K14" s="10"/>
-    </row>
-    <row r="15" spans="1:11" ht="15" x14ac:dyDescent="0.2">
-      <c r="A15" s="9"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10"/>
-    </row>
-    <row r="16" spans="1:11" ht="15" x14ac:dyDescent="0.2">
-      <c r="A16" s="9"/>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
-      <c r="I16" s="10"/>
-      <c r="J16" s="10"/>
-      <c r="K16" s="10"/>
-    </row>
-    <row r="17" spans="1:11" ht="15" x14ac:dyDescent="0.2">
-      <c r="A17" s="9"/>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
-      <c r="I17" s="10"/>
-      <c r="J17" s="10"/>
-      <c r="K17" s="10"/>
-    </row>
-    <row r="18" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
-      <c r="I18" s="5"/>
-      <c r="J18" s="5"/>
-      <c r="K18" s="5"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>1</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G19" s="1" t="e">
         <f t="shared" ref="G19:G38" si="0">IF(D19=0,"",ROUND(E19/D19*100,2))</f>
@@ -924,26 +938,26 @@
         <v>2</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G20" s="1" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
@@ -954,19 +968,19 @@
         <v>3</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G21" s="1" t="e">
         <f t="shared" si="0"/>
@@ -982,19 +996,19 @@
         <v>4</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G22" s="1" t="e">
         <f t="shared" si="0"/>
@@ -1010,19 +1024,19 @@
         <v>5</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G23" s="1" t="e">
         <f t="shared" si="0"/>
@@ -1038,19 +1052,19 @@
         <v>6</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G24" s="1" t="e">
         <f t="shared" si="0"/>
@@ -1066,19 +1080,19 @@
         <v>7</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G25" s="1" t="e">
         <f t="shared" si="0"/>
@@ -1094,19 +1108,19 @@
         <v>8</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G26" s="1" t="e">
         <f t="shared" si="0"/>
@@ -1122,19 +1136,19 @@
         <v>9</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G27" s="1" t="e">
         <f t="shared" si="0"/>
@@ -1150,19 +1164,19 @@
         <v>10</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G28" s="1" t="e">
         <f t="shared" si="0"/>
@@ -1178,19 +1192,19 @@
         <v>11</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G29" s="1" t="e">
         <f t="shared" si="0"/>
@@ -1363,26 +1377,8 @@
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
     </row>
-    <row r="40" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A40" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B40" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C40" s="12"/>
-      <c r="D40" s="12"/>
-      <c r="E40" s="12"/>
-      <c r="F40" s="12"/>
-      <c r="G40" s="12"/>
-      <c r="H40" s="12"/>
-      <c r="I40" s="12"/>
-      <c r="J40" s="12"/>
-      <c r="K40" s="12"/>
-    </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B40:K40"/>
+  <mergeCells count="1">
     <mergeCell ref="A1:K1"/>
   </mergeCells>
   <dataValidations count="6">
@@ -1413,7 +1409,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -1422,43 +1418,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="4" t="s">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" s="7" t="s">
-        <v>20</v>
-      </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B16" t="s">
         <v>37</v>
       </c>
     </row>
